--- a/Results/single_algorithm/wMKL/wMKL_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
+++ b/Results/single_algorithm/wMKL/wMKL_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
@@ -23,126 +23,129 @@
     <t xml:space="preserve">TCGA-AQ-A0Y5-01A</t>
   </si>
   <si>
+    <t xml:space="preserve">wMKL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A2FW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wMKL8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A274-01A</t>
+  </si>
+  <si>
     <t xml:space="preserve">wMKL6</t>
   </si>
   <si>
-    <t xml:space="preserve">TCGA-EW-A2FW-01A</t>
+    <t xml:space="preserve">TCGA-B6-A0IK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1L7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A247-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0SV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wMKL7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2FG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AQ-A7U7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wMKL4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1Y2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1B1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A23E-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A278-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A3W7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wMKL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1PH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A6R8-01A</t>
   </si>
   <si>
     <t xml:space="preserve">wMKL2</t>
   </si>
   <si>
-    <t xml:space="preserve">TCGA-C8-A274-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wMKL7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0IK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1L7-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A247-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0SV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wMKL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2FG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wMKL8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AQ-A7U7-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1Y2-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1B1-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WX-01A</t>
+    <t xml:space="preserve">TCGA-D8-A27W-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0U2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0H9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-W8-A86G-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0B6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A5UO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24H-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A15I-01A</t>
   </si>
   <si>
     <t xml:space="preserve">wMKL5</t>
   </si>
   <si>
-    <t xml:space="preserve">TCGA-AC-A23E-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A278-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A3W7-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wMKL4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1PH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A6R8-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27W-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0U2-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0H9-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-W8-A86G-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0B6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A5UO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24H-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A15I-01A</t>
-  </si>
-  <si>
     <t xml:space="preserve">TCGA-AC-A2BK-01A</t>
   </si>
   <si>
@@ -186,9 +189,6 @@
   </si>
   <si>
     <t xml:space="preserve">TCGA-A7-A26E-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wMKL1</t>
   </si>
   <si>
     <t xml:space="preserve">TCGA-E2-A1IU-01A</t>
@@ -2314,12 +2314,12 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
         <v>5</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -2338,20 +2338,20 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
@@ -2359,10 +2359,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -2370,7 +2370,7 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -2386,12 +2386,12 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
@@ -2399,34 +2399,34 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
         <v>27</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="s">
         <v>30</v>
-      </c>
-      <c r="B23" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2442,7 +2442,7 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -2466,7 +2466,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -2482,7 +2482,7 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -2522,20 +2522,20 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
         <v>7</v>
@@ -2543,55 +2543,55 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
         <v>3</v>
@@ -2599,15 +2599,15 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B46" t="s">
         <v>3</v>
@@ -2615,15 +2615,15 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B48" t="s">
         <v>5</v>
@@ -2631,7 +2631,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B49" t="s">
         <v>5</v>
@@ -2639,10 +2639,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51">
@@ -2650,7 +2650,7 @@
         <v>59</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52">
@@ -2658,7 +2658,7 @@
         <v>60</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -2674,7 +2674,7 @@
         <v>62</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
@@ -2682,7 +2682,7 @@
         <v>63</v>
       </c>
       <c r="B55" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56">
@@ -2698,7 +2698,7 @@
         <v>65</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -2706,7 +2706,7 @@
         <v>66</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59">
@@ -2714,7 +2714,7 @@
         <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
@@ -2722,7 +2722,7 @@
         <v>68</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61">
@@ -2730,7 +2730,7 @@
         <v>69</v>
       </c>
       <c r="B61" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -2738,7 +2738,7 @@
         <v>70</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63">
@@ -2746,7 +2746,7 @@
         <v>71</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
@@ -2754,7 +2754,7 @@
         <v>72</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
@@ -2778,7 +2778,7 @@
         <v>75</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68">
@@ -2786,7 +2786,7 @@
         <v>76</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69">
@@ -2794,7 +2794,7 @@
         <v>77</v>
       </c>
       <c r="B69" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
@@ -2802,7 +2802,7 @@
         <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71">
@@ -2810,7 +2810,7 @@
         <v>79</v>
       </c>
       <c r="B71" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72">
@@ -2826,7 +2826,7 @@
         <v>81</v>
       </c>
       <c r="B73" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -2842,7 +2842,7 @@
         <v>83</v>
       </c>
       <c r="B75" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76">
@@ -2858,7 +2858,7 @@
         <v>85</v>
       </c>
       <c r="B77" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78">
@@ -2866,7 +2866,7 @@
         <v>86</v>
       </c>
       <c r="B78" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -2874,7 +2874,7 @@
         <v>87</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80">
@@ -2882,7 +2882,7 @@
         <v>88</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81">
@@ -2890,7 +2890,7 @@
         <v>89</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82">
@@ -2898,7 +2898,7 @@
         <v>90</v>
       </c>
       <c r="B82" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83">
@@ -2922,7 +2922,7 @@
         <v>93</v>
       </c>
       <c r="B85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86">
@@ -2930,7 +2930,7 @@
         <v>94</v>
       </c>
       <c r="B86" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87">
@@ -2946,7 +2946,7 @@
         <v>96</v>
       </c>
       <c r="B88" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89">
@@ -2954,7 +2954,7 @@
         <v>97</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
@@ -2962,7 +2962,7 @@
         <v>98</v>
       </c>
       <c r="B90" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91">
@@ -2970,7 +2970,7 @@
         <v>99</v>
       </c>
       <c r="B91" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92">
@@ -2986,7 +2986,7 @@
         <v>101</v>
       </c>
       <c r="B93" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94">
@@ -3002,7 +3002,7 @@
         <v>103</v>
       </c>
       <c r="B95" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96">
@@ -3042,7 +3042,7 @@
         <v>108</v>
       </c>
       <c r="B100" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="101">
@@ -3050,7 +3050,7 @@
         <v>109</v>
       </c>
       <c r="B101" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -3058,7 +3058,7 @@
         <v>110</v>
       </c>
       <c r="B102" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103">
@@ -3074,7 +3074,7 @@
         <v>112</v>
       </c>
       <c r="B104" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105">
@@ -3090,7 +3090,7 @@
         <v>114</v>
       </c>
       <c r="B106" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107">
@@ -3098,7 +3098,7 @@
         <v>115</v>
       </c>
       <c r="B107" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="108">
@@ -3138,7 +3138,7 @@
         <v>120</v>
       </c>
       <c r="B112" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113">
@@ -3154,7 +3154,7 @@
         <v>122</v>
       </c>
       <c r="B114" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115">
@@ -3170,7 +3170,7 @@
         <v>124</v>
       </c>
       <c r="B116" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
@@ -3178,7 +3178,7 @@
         <v>125</v>
       </c>
       <c r="B117" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
@@ -3186,7 +3186,7 @@
         <v>126</v>
       </c>
       <c r="B118" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="119">
@@ -3194,7 +3194,7 @@
         <v>127</v>
       </c>
       <c r="B119" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120">
@@ -3210,7 +3210,7 @@
         <v>129</v>
       </c>
       <c r="B121" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="122">
@@ -3242,7 +3242,7 @@
         <v>133</v>
       </c>
       <c r="B125" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
@@ -3250,7 +3250,7 @@
         <v>134</v>
       </c>
       <c r="B126" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">
@@ -3266,7 +3266,7 @@
         <v>136</v>
       </c>
       <c r="B128" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="129">
@@ -3282,7 +3282,7 @@
         <v>138</v>
       </c>
       <c r="B130" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
@@ -3290,7 +3290,7 @@
         <v>139</v>
       </c>
       <c r="B131" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="132">
@@ -3298,7 +3298,7 @@
         <v>140</v>
       </c>
       <c r="B132" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
@@ -3306,7 +3306,7 @@
         <v>141</v>
       </c>
       <c r="B133" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134">
@@ -3314,7 +3314,7 @@
         <v>142</v>
       </c>
       <c r="B134" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135">
@@ -3322,7 +3322,7 @@
         <v>143</v>
       </c>
       <c r="B135" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136">
@@ -3330,7 +3330,7 @@
         <v>144</v>
       </c>
       <c r="B136" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137">
@@ -3338,7 +3338,7 @@
         <v>145</v>
       </c>
       <c r="B137" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138">
@@ -3354,7 +3354,7 @@
         <v>147</v>
       </c>
       <c r="B139" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="140">
@@ -3362,7 +3362,7 @@
         <v>148</v>
       </c>
       <c r="B140" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="141">
@@ -3378,7 +3378,7 @@
         <v>150</v>
       </c>
       <c r="B142" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="143">
@@ -3386,7 +3386,7 @@
         <v>151</v>
       </c>
       <c r="B143" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
@@ -3394,7 +3394,7 @@
         <v>152</v>
       </c>
       <c r="B144" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="145">
@@ -3402,7 +3402,7 @@
         <v>153</v>
       </c>
       <c r="B145" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
@@ -3410,7 +3410,7 @@
         <v>154</v>
       </c>
       <c r="B146" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147">
@@ -3426,7 +3426,7 @@
         <v>156</v>
       </c>
       <c r="B148" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149">
@@ -3434,7 +3434,7 @@
         <v>157</v>
       </c>
       <c r="B149" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150">
@@ -3450,7 +3450,7 @@
         <v>159</v>
       </c>
       <c r="B151" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="152">
@@ -3458,7 +3458,7 @@
         <v>160</v>
       </c>
       <c r="B152" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="153">
@@ -3466,7 +3466,7 @@
         <v>161</v>
       </c>
       <c r="B153" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154">
@@ -3474,7 +3474,7 @@
         <v>162</v>
       </c>
       <c r="B154" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="155">
@@ -3482,7 +3482,7 @@
         <v>163</v>
       </c>
       <c r="B155" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="156">
@@ -3490,7 +3490,7 @@
         <v>164</v>
       </c>
       <c r="B156" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157">
@@ -3498,7 +3498,7 @@
         <v>165</v>
       </c>
       <c r="B157" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="158">
@@ -3522,7 +3522,7 @@
         <v>168</v>
       </c>
       <c r="B160" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161">
@@ -3530,7 +3530,7 @@
         <v>169</v>
       </c>
       <c r="B161" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162">
@@ -3538,7 +3538,7 @@
         <v>170</v>
       </c>
       <c r="B162" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="163">
@@ -3546,7 +3546,7 @@
         <v>171</v>
       </c>
       <c r="B163" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="164">
@@ -3554,7 +3554,7 @@
         <v>172</v>
       </c>
       <c r="B164" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165">
@@ -3562,7 +3562,7 @@
         <v>173</v>
       </c>
       <c r="B165" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166">
@@ -3570,7 +3570,7 @@
         <v>174</v>
       </c>
       <c r="B166" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167">
@@ -3578,7 +3578,7 @@
         <v>175</v>
       </c>
       <c r="B167" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168">
@@ -3586,7 +3586,7 @@
         <v>176</v>
       </c>
       <c r="B168" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="169">
@@ -3594,7 +3594,7 @@
         <v>177</v>
       </c>
       <c r="B169" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="170">
@@ -3610,7 +3610,7 @@
         <v>179</v>
       </c>
       <c r="B171" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="172">
@@ -3618,7 +3618,7 @@
         <v>180</v>
       </c>
       <c r="B172" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173">
@@ -3626,7 +3626,7 @@
         <v>181</v>
       </c>
       <c r="B173" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="174">
@@ -3642,7 +3642,7 @@
         <v>183</v>
       </c>
       <c r="B175" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176">
@@ -3658,7 +3658,7 @@
         <v>185</v>
       </c>
       <c r="B177" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="178">
@@ -3674,7 +3674,7 @@
         <v>187</v>
       </c>
       <c r="B179" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180">
@@ -3682,7 +3682,7 @@
         <v>188</v>
       </c>
       <c r="B180" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="181">
@@ -3690,7 +3690,7 @@
         <v>189</v>
       </c>
       <c r="B181" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="182">
@@ -3698,7 +3698,7 @@
         <v>190</v>
       </c>
       <c r="B182" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183">
@@ -3706,7 +3706,7 @@
         <v>191</v>
       </c>
       <c r="B183" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184">
@@ -3722,7 +3722,7 @@
         <v>193</v>
       </c>
       <c r="B185" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186">
@@ -3730,7 +3730,7 @@
         <v>194</v>
       </c>
       <c r="B186" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="187">
@@ -3738,7 +3738,7 @@
         <v>195</v>
       </c>
       <c r="B187" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="188">
@@ -3754,7 +3754,7 @@
         <v>197</v>
       </c>
       <c r="B189" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190">
@@ -3762,7 +3762,7 @@
         <v>198</v>
       </c>
       <c r="B190" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="191">
@@ -3778,7 +3778,7 @@
         <v>200</v>
       </c>
       <c r="B192" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193">
@@ -3794,7 +3794,7 @@
         <v>202</v>
       </c>
       <c r="B194" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195">
@@ -3810,7 +3810,7 @@
         <v>204</v>
       </c>
       <c r="B196" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197">
@@ -3866,7 +3866,7 @@
         <v>211</v>
       </c>
       <c r="B203" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204">
@@ -3882,7 +3882,7 @@
         <v>213</v>
       </c>
       <c r="B205" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="206">
@@ -3898,7 +3898,7 @@
         <v>215</v>
       </c>
       <c r="B207" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="208">
@@ -3914,7 +3914,7 @@
         <v>217</v>
       </c>
       <c r="B209" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="210">
@@ -3922,7 +3922,7 @@
         <v>218</v>
       </c>
       <c r="B210" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="211">
@@ -3930,7 +3930,7 @@
         <v>219</v>
       </c>
       <c r="B211" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212">
@@ -3946,7 +3946,7 @@
         <v>221</v>
       </c>
       <c r="B213" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214">
@@ -3954,7 +3954,7 @@
         <v>222</v>
       </c>
       <c r="B214" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215">
@@ -3962,7 +3962,7 @@
         <v>223</v>
       </c>
       <c r="B215" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216">
@@ -3970,7 +3970,7 @@
         <v>224</v>
       </c>
       <c r="B216" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="217">
@@ -3986,7 +3986,7 @@
         <v>226</v>
       </c>
       <c r="B218" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219">
@@ -3994,7 +3994,7 @@
         <v>227</v>
       </c>
       <c r="B219" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="220">
@@ -4010,7 +4010,7 @@
         <v>229</v>
       </c>
       <c r="B221" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222">
@@ -4018,7 +4018,7 @@
         <v>230</v>
       </c>
       <c r="B222" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="223">
@@ -4026,7 +4026,7 @@
         <v>231</v>
       </c>
       <c r="B223" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="224">
@@ -4042,7 +4042,7 @@
         <v>233</v>
       </c>
       <c r="B225" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="226">
@@ -4050,7 +4050,7 @@
         <v>234</v>
       </c>
       <c r="B226" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="227">
@@ -4058,7 +4058,7 @@
         <v>235</v>
       </c>
       <c r="B227" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="228">
@@ -4066,7 +4066,7 @@
         <v>236</v>
       </c>
       <c r="B228" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="229">
@@ -4074,7 +4074,7 @@
         <v>237</v>
       </c>
       <c r="B229" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="230">
@@ -4082,7 +4082,7 @@
         <v>238</v>
       </c>
       <c r="B230" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="231">
@@ -4090,7 +4090,7 @@
         <v>239</v>
       </c>
       <c r="B231" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232">
@@ -4098,7 +4098,7 @@
         <v>240</v>
       </c>
       <c r="B232" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="233">
@@ -4122,7 +4122,7 @@
         <v>243</v>
       </c>
       <c r="B235" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="236">
@@ -4146,7 +4146,7 @@
         <v>246</v>
       </c>
       <c r="B238" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="239">
@@ -4170,7 +4170,7 @@
         <v>249</v>
       </c>
       <c r="B241" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="242">
@@ -4178,7 +4178,7 @@
         <v>250</v>
       </c>
       <c r="B242" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243">
@@ -4194,7 +4194,7 @@
         <v>252</v>
       </c>
       <c r="B244" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245">
@@ -4202,7 +4202,7 @@
         <v>253</v>
       </c>
       <c r="B245" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246">
@@ -4218,7 +4218,7 @@
         <v>255</v>
       </c>
       <c r="B247" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="248">
@@ -4226,7 +4226,7 @@
         <v>256</v>
       </c>
       <c r="B248" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="249">
@@ -4234,7 +4234,7 @@
         <v>257</v>
       </c>
       <c r="B249" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250">
@@ -4250,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="B251" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="252">
@@ -4258,7 +4258,7 @@
         <v>260</v>
       </c>
       <c r="B252" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="253">
@@ -4266,7 +4266,7 @@
         <v>261</v>
       </c>
       <c r="B253" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254">
@@ -4290,7 +4290,7 @@
         <v>264</v>
       </c>
       <c r="B256" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="257">
@@ -4298,7 +4298,7 @@
         <v>265</v>
       </c>
       <c r="B257" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258">
@@ -4322,7 +4322,7 @@
         <v>268</v>
       </c>
       <c r="B260" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="261">
@@ -4330,7 +4330,7 @@
         <v>269</v>
       </c>
       <c r="B261" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="262">
@@ -4338,7 +4338,7 @@
         <v>270</v>
       </c>
       <c r="B262" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="263">
@@ -4346,7 +4346,7 @@
         <v>271</v>
       </c>
       <c r="B263" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="264">
@@ -4354,7 +4354,7 @@
         <v>272</v>
       </c>
       <c r="B264" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265">
@@ -4362,7 +4362,7 @@
         <v>273</v>
       </c>
       <c r="B265" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="266">
@@ -4370,7 +4370,7 @@
         <v>274</v>
       </c>
       <c r="B266" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="267">
@@ -4378,7 +4378,7 @@
         <v>275</v>
       </c>
       <c r="B267" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="268">
@@ -4394,7 +4394,7 @@
         <v>277</v>
       </c>
       <c r="B269" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="270">
@@ -4426,7 +4426,7 @@
         <v>281</v>
       </c>
       <c r="B273" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="274">
@@ -4434,7 +4434,7 @@
         <v>282</v>
       </c>
       <c r="B274" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275">
@@ -4442,7 +4442,7 @@
         <v>283</v>
       </c>
       <c r="B275" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="276">
@@ -4458,7 +4458,7 @@
         <v>285</v>
       </c>
       <c r="B277" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="278">
@@ -4466,7 +4466,7 @@
         <v>286</v>
       </c>
       <c r="B278" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279">
@@ -4474,7 +4474,7 @@
         <v>287</v>
       </c>
       <c r="B279" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="280">
@@ -4490,7 +4490,7 @@
         <v>289</v>
       </c>
       <c r="B281" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="282">
@@ -4498,7 +4498,7 @@
         <v>290</v>
       </c>
       <c r="B282" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="283">
@@ -4506,7 +4506,7 @@
         <v>291</v>
       </c>
       <c r="B283" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="284">
@@ -4514,7 +4514,7 @@
         <v>292</v>
       </c>
       <c r="B284" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285">
@@ -4530,7 +4530,7 @@
         <v>294</v>
       </c>
       <c r="B286" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287">
@@ -4538,7 +4538,7 @@
         <v>295</v>
       </c>
       <c r="B287" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="288">
@@ -4578,7 +4578,7 @@
         <v>300</v>
       </c>
       <c r="B292" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="293">
@@ -4586,7 +4586,7 @@
         <v>301</v>
       </c>
       <c r="B293" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="294">
@@ -4594,7 +4594,7 @@
         <v>302</v>
       </c>
       <c r="B294" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="295">
@@ -4610,7 +4610,7 @@
         <v>304</v>
       </c>
       <c r="B296" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="297">
@@ -4618,7 +4618,7 @@
         <v>305</v>
       </c>
       <c r="B297" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="298">
@@ -4626,7 +4626,7 @@
         <v>306</v>
       </c>
       <c r="B298" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="299">
@@ -4634,7 +4634,7 @@
         <v>307</v>
       </c>
       <c r="B299" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="300">
@@ -4650,7 +4650,7 @@
         <v>309</v>
       </c>
       <c r="B301" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="302">
@@ -4666,7 +4666,7 @@
         <v>311</v>
       </c>
       <c r="B303" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="304">
@@ -4674,7 +4674,7 @@
         <v>312</v>
       </c>
       <c r="B304" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="305">
@@ -4682,7 +4682,7 @@
         <v>313</v>
       </c>
       <c r="B305" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="306">
@@ -4690,7 +4690,7 @@
         <v>314</v>
       </c>
       <c r="B306" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="307">
@@ -4698,7 +4698,7 @@
         <v>315</v>
       </c>
       <c r="B307" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="308">
@@ -4706,7 +4706,7 @@
         <v>316</v>
       </c>
       <c r="B308" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="309">
@@ -4714,7 +4714,7 @@
         <v>317</v>
       </c>
       <c r="B309" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="310">
@@ -4730,7 +4730,7 @@
         <v>319</v>
       </c>
       <c r="B311" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="312">
@@ -4746,7 +4746,7 @@
         <v>321</v>
       </c>
       <c r="B313" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="314">
@@ -4754,7 +4754,7 @@
         <v>322</v>
       </c>
       <c r="B314" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="315">
@@ -4762,7 +4762,7 @@
         <v>323</v>
       </c>
       <c r="B315" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="316">
@@ -4770,7 +4770,7 @@
         <v>324</v>
       </c>
       <c r="B316" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="317">
@@ -4778,7 +4778,7 @@
         <v>325</v>
       </c>
       <c r="B317" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="318">
@@ -4786,7 +4786,7 @@
         <v>326</v>
       </c>
       <c r="B318" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="319">
@@ -4794,7 +4794,7 @@
         <v>327</v>
       </c>
       <c r="B319" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320">
@@ -4802,7 +4802,7 @@
         <v>328</v>
       </c>
       <c r="B320" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="321">
@@ -4810,7 +4810,7 @@
         <v>329</v>
       </c>
       <c r="B321" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="322">
@@ -4818,7 +4818,7 @@
         <v>330</v>
       </c>
       <c r="B322" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="323">
@@ -4826,7 +4826,7 @@
         <v>331</v>
       </c>
       <c r="B323" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="324">
@@ -4834,7 +4834,7 @@
         <v>332</v>
       </c>
       <c r="B324" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="325">
@@ -4842,7 +4842,7 @@
         <v>333</v>
       </c>
       <c r="B325" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326">
@@ -4850,7 +4850,7 @@
         <v>334</v>
       </c>
       <c r="B326" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="327">
@@ -4866,7 +4866,7 @@
         <v>336</v>
       </c>
       <c r="B328" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="329">
@@ -4874,7 +4874,7 @@
         <v>337</v>
       </c>
       <c r="B329" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="330">
@@ -4882,7 +4882,7 @@
         <v>338</v>
       </c>
       <c r="B330" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="331">
@@ -4890,7 +4890,7 @@
         <v>339</v>
       </c>
       <c r="B331" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="332">
@@ -4898,7 +4898,7 @@
         <v>340</v>
       </c>
       <c r="B332" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="333">
@@ -4906,7 +4906,7 @@
         <v>341</v>
       </c>
       <c r="B333" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="334">
@@ -4914,7 +4914,7 @@
         <v>342</v>
       </c>
       <c r="B334" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="335">
@@ -4930,7 +4930,7 @@
         <v>344</v>
       </c>
       <c r="B336" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="337">
@@ -4938,7 +4938,7 @@
         <v>345</v>
       </c>
       <c r="B337" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="338">
@@ -4946,7 +4946,7 @@
         <v>346</v>
       </c>
       <c r="B338" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="339">
@@ -4954,7 +4954,7 @@
         <v>347</v>
       </c>
       <c r="B339" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="340">
@@ -4962,7 +4962,7 @@
         <v>348</v>
       </c>
       <c r="B340" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="341">
@@ -4978,7 +4978,7 @@
         <v>350</v>
       </c>
       <c r="B342" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="343">
@@ -4986,7 +4986,7 @@
         <v>351</v>
       </c>
       <c r="B343" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="344">
@@ -5002,7 +5002,7 @@
         <v>353</v>
       </c>
       <c r="B345" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="346">
@@ -5018,7 +5018,7 @@
         <v>355</v>
       </c>
       <c r="B347" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="348">
@@ -5034,7 +5034,7 @@
         <v>357</v>
       </c>
       <c r="B349" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="350">
@@ -5058,7 +5058,7 @@
         <v>360</v>
       </c>
       <c r="B352" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="353">
@@ -5066,7 +5066,7 @@
         <v>361</v>
       </c>
       <c r="B353" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="354">
@@ -5074,7 +5074,7 @@
         <v>362</v>
       </c>
       <c r="B354" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="355">
@@ -5090,7 +5090,7 @@
         <v>364</v>
       </c>
       <c r="B356" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="357">
@@ -5106,7 +5106,7 @@
         <v>366</v>
       </c>
       <c r="B358" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="359">
@@ -5122,7 +5122,7 @@
         <v>368</v>
       </c>
       <c r="B360" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="361">
@@ -5130,7 +5130,7 @@
         <v>369</v>
       </c>
       <c r="B361" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="362">
@@ -5154,7 +5154,7 @@
         <v>372</v>
       </c>
       <c r="B364" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="365">
@@ -5170,7 +5170,7 @@
         <v>374</v>
       </c>
       <c r="B366" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="367">
@@ -5178,7 +5178,7 @@
         <v>375</v>
       </c>
       <c r="B367" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="368">
@@ -5186,7 +5186,7 @@
         <v>376</v>
       </c>
       <c r="B368" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="369">
@@ -5202,7 +5202,7 @@
         <v>378</v>
       </c>
       <c r="B370" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="371">
@@ -5210,7 +5210,7 @@
         <v>379</v>
       </c>
       <c r="B371" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="372">
@@ -5234,7 +5234,7 @@
         <v>382</v>
       </c>
       <c r="B374" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="375">
@@ -5250,7 +5250,7 @@
         <v>384</v>
       </c>
       <c r="B376" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="377">
@@ -5266,7 +5266,7 @@
         <v>386</v>
       </c>
       <c r="B378" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="379">
@@ -5274,7 +5274,7 @@
         <v>387</v>
       </c>
       <c r="B379" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="380">
@@ -5282,7 +5282,7 @@
         <v>388</v>
       </c>
       <c r="B380" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="381">
@@ -5298,7 +5298,7 @@
         <v>390</v>
       </c>
       <c r="B382" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="383">
@@ -5314,7 +5314,7 @@
         <v>392</v>
       </c>
       <c r="B384" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="385">
@@ -5322,7 +5322,7 @@
         <v>393</v>
       </c>
       <c r="B385" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="386">
@@ -5330,7 +5330,7 @@
         <v>394</v>
       </c>
       <c r="B386" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="387">
@@ -5362,7 +5362,7 @@
         <v>398</v>
       </c>
       <c r="B390" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="391">
@@ -5370,7 +5370,7 @@
         <v>399</v>
       </c>
       <c r="B391" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="392">
@@ -5378,7 +5378,7 @@
         <v>400</v>
       </c>
       <c r="B392" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="393">
@@ -5394,7 +5394,7 @@
         <v>402</v>
       </c>
       <c r="B394" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="395">
@@ -5402,7 +5402,7 @@
         <v>403</v>
       </c>
       <c r="B395" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="396">
@@ -5410,7 +5410,7 @@
         <v>404</v>
       </c>
       <c r="B396" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="397">
@@ -5418,7 +5418,7 @@
         <v>405</v>
       </c>
       <c r="B397" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="398">
@@ -5434,7 +5434,7 @@
         <v>407</v>
       </c>
       <c r="B399" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="400">
@@ -5458,7 +5458,7 @@
         <v>410</v>
       </c>
       <c r="B402" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="403">
@@ -5474,7 +5474,7 @@
         <v>412</v>
       </c>
       <c r="B404" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="405">
@@ -5490,7 +5490,7 @@
         <v>414</v>
       </c>
       <c r="B406" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="407">
@@ -5498,7 +5498,7 @@
         <v>415</v>
       </c>
       <c r="B407" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="408">
@@ -5506,7 +5506,7 @@
         <v>416</v>
       </c>
       <c r="B408" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="409">
@@ -5514,7 +5514,7 @@
         <v>417</v>
       </c>
       <c r="B409" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="410">
@@ -5522,7 +5522,7 @@
         <v>418</v>
       </c>
       <c r="B410" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="411">
@@ -5530,7 +5530,7 @@
         <v>419</v>
       </c>
       <c r="B411" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="412">
@@ -5546,7 +5546,7 @@
         <v>421</v>
       </c>
       <c r="B413" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="414">
@@ -5554,7 +5554,7 @@
         <v>422</v>
       </c>
       <c r="B414" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="415">
@@ -5562,7 +5562,7 @@
         <v>423</v>
       </c>
       <c r="B415" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="416">
@@ -5570,7 +5570,7 @@
         <v>424</v>
       </c>
       <c r="B416" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="417">
@@ -5578,7 +5578,7 @@
         <v>425</v>
       </c>
       <c r="B417" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="418">
@@ -5586,7 +5586,7 @@
         <v>426</v>
       </c>
       <c r="B418" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="419">
@@ -5594,7 +5594,7 @@
         <v>427</v>
       </c>
       <c r="B419" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="420">
@@ -5602,7 +5602,7 @@
         <v>428</v>
       </c>
       <c r="B420" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="421">
@@ -5610,7 +5610,7 @@
         <v>429</v>
       </c>
       <c r="B421" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="422">
@@ -5618,7 +5618,7 @@
         <v>430</v>
       </c>
       <c r="B422" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="423">
@@ -5626,7 +5626,7 @@
         <v>431</v>
       </c>
       <c r="B423" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="424">
@@ -5642,7 +5642,7 @@
         <v>433</v>
       </c>
       <c r="B425" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="426">
@@ -5650,7 +5650,7 @@
         <v>434</v>
       </c>
       <c r="B426" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="427">
@@ -5658,7 +5658,7 @@
         <v>435</v>
       </c>
       <c r="B427" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="428">
@@ -5674,7 +5674,7 @@
         <v>437</v>
       </c>
       <c r="B429" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="430">
@@ -5682,7 +5682,7 @@
         <v>438</v>
       </c>
       <c r="B430" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="431">
@@ -5690,7 +5690,7 @@
         <v>439</v>
       </c>
       <c r="B431" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="432">
@@ -5698,7 +5698,7 @@
         <v>440</v>
       </c>
       <c r="B432" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="433">
@@ -5706,7 +5706,7 @@
         <v>441</v>
       </c>
       <c r="B433" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="434">
@@ -5714,7 +5714,7 @@
         <v>442</v>
       </c>
       <c r="B434" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="435">
@@ -5722,7 +5722,7 @@
         <v>443</v>
       </c>
       <c r="B435" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="436">
@@ -5730,7 +5730,7 @@
         <v>444</v>
       </c>
       <c r="B436" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="437">
@@ -5738,7 +5738,7 @@
         <v>445</v>
       </c>
       <c r="B437" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="438">
@@ -5754,7 +5754,7 @@
         <v>447</v>
       </c>
       <c r="B439" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="440">
@@ -5770,7 +5770,7 @@
         <v>449</v>
       </c>
       <c r="B441" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="442">
@@ -5786,7 +5786,7 @@
         <v>451</v>
       </c>
       <c r="B443" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="444">
@@ -5810,7 +5810,7 @@
         <v>454</v>
       </c>
       <c r="B446" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="447">
@@ -5818,7 +5818,7 @@
         <v>455</v>
       </c>
       <c r="B447" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="448">
@@ -5826,7 +5826,7 @@
         <v>456</v>
       </c>
       <c r="B448" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="449">
@@ -5834,7 +5834,7 @@
         <v>457</v>
       </c>
       <c r="B449" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="450">
@@ -5842,7 +5842,7 @@
         <v>458</v>
       </c>
       <c r="B450" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="451">
@@ -5850,7 +5850,7 @@
         <v>459</v>
       </c>
       <c r="B451" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="452">
@@ -5858,7 +5858,7 @@
         <v>460</v>
       </c>
       <c r="B452" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="453">
@@ -5882,7 +5882,7 @@
         <v>463</v>
       </c>
       <c r="B455" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="456">
@@ -5898,7 +5898,7 @@
         <v>465</v>
       </c>
       <c r="B457" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="458">
@@ -5938,7 +5938,7 @@
         <v>470</v>
       </c>
       <c r="B462" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="463">
@@ -5946,7 +5946,7 @@
         <v>471</v>
       </c>
       <c r="B463" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="464">
@@ -5962,7 +5962,7 @@
         <v>473</v>
       </c>
       <c r="B465" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="466">
@@ -5970,7 +5970,7 @@
         <v>474</v>
       </c>
       <c r="B466" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="467">
@@ -5986,7 +5986,7 @@
         <v>476</v>
       </c>
       <c r="B468" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="469">
@@ -5994,7 +5994,7 @@
         <v>477</v>
       </c>
       <c r="B469" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="470">
@@ -6018,7 +6018,7 @@
         <v>480</v>
       </c>
       <c r="B472" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="473">
@@ -6026,7 +6026,7 @@
         <v>481</v>
       </c>
       <c r="B473" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="474">
@@ -6034,7 +6034,7 @@
         <v>482</v>
       </c>
       <c r="B474" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="475">
@@ -6042,7 +6042,7 @@
         <v>483</v>
       </c>
       <c r="B475" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="476">
@@ -6050,7 +6050,7 @@
         <v>484</v>
       </c>
       <c r="B476" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="477">
@@ -6058,7 +6058,7 @@
         <v>485</v>
       </c>
       <c r="B477" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="478">
@@ -6090,7 +6090,7 @@
         <v>489</v>
       </c>
       <c r="B481" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="482">
@@ -6098,7 +6098,7 @@
         <v>490</v>
       </c>
       <c r="B482" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="483">
@@ -6114,7 +6114,7 @@
         <v>492</v>
       </c>
       <c r="B484" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="485">
@@ -6122,7 +6122,7 @@
         <v>493</v>
       </c>
       <c r="B485" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="486">
@@ -6130,7 +6130,7 @@
         <v>494</v>
       </c>
       <c r="B486" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="487">
@@ -6138,7 +6138,7 @@
         <v>495</v>
       </c>
       <c r="B487" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="488">
@@ -6146,7 +6146,7 @@
         <v>496</v>
       </c>
       <c r="B488" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="489">
@@ -6178,7 +6178,7 @@
         <v>500</v>
       </c>
       <c r="B492" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="493">
@@ -6186,7 +6186,7 @@
         <v>501</v>
       </c>
       <c r="B493" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="494">
@@ -6202,7 +6202,7 @@
         <v>503</v>
       </c>
       <c r="B495" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="496">
@@ -6210,7 +6210,7 @@
         <v>504</v>
       </c>
       <c r="B496" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="497">
@@ -6218,7 +6218,7 @@
         <v>505</v>
       </c>
       <c r="B497" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="498">
@@ -6226,7 +6226,7 @@
         <v>506</v>
       </c>
       <c r="B498" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="499">
@@ -6234,7 +6234,7 @@
         <v>507</v>
       </c>
       <c r="B499" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="500">
@@ -6274,7 +6274,7 @@
         <v>512</v>
       </c>
       <c r="B504" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="505">
@@ -6290,7 +6290,7 @@
         <v>514</v>
       </c>
       <c r="B506" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="507">
@@ -6298,7 +6298,7 @@
         <v>515</v>
       </c>
       <c r="B507" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="508">
@@ -6322,7 +6322,7 @@
         <v>518</v>
       </c>
       <c r="B510" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="511">
@@ -6330,7 +6330,7 @@
         <v>519</v>
       </c>
       <c r="B511" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="512">
@@ -6346,7 +6346,7 @@
         <v>521</v>
       </c>
       <c r="B513" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="514">
@@ -6362,7 +6362,7 @@
         <v>523</v>
       </c>
       <c r="B515" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="516">
@@ -6370,7 +6370,7 @@
         <v>524</v>
       </c>
       <c r="B516" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="517">
@@ -6378,7 +6378,7 @@
         <v>525</v>
       </c>
       <c r="B517" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="518">
@@ -6386,7 +6386,7 @@
         <v>526</v>
       </c>
       <c r="B518" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="519">
@@ -6394,7 +6394,7 @@
         <v>527</v>
       </c>
       <c r="B519" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="520">
@@ -6410,7 +6410,7 @@
         <v>529</v>
       </c>
       <c r="B521" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="522">
@@ -6418,7 +6418,7 @@
         <v>530</v>
       </c>
       <c r="B522" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="523">
@@ -6426,7 +6426,7 @@
         <v>531</v>
       </c>
       <c r="B523" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="524">
@@ -6434,7 +6434,7 @@
         <v>532</v>
       </c>
       <c r="B524" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="525">
@@ -6450,7 +6450,7 @@
         <v>534</v>
       </c>
       <c r="B526" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="527">
@@ -6458,7 +6458,7 @@
         <v>535</v>
       </c>
       <c r="B527" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="528">
@@ -6466,7 +6466,7 @@
         <v>536</v>
       </c>
       <c r="B528" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="529">
@@ -6490,7 +6490,7 @@
         <v>539</v>
       </c>
       <c r="B531" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="532">
@@ -6506,7 +6506,7 @@
         <v>541</v>
       </c>
       <c r="B533" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="534">
@@ -6514,7 +6514,7 @@
         <v>542</v>
       </c>
       <c r="B534" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="535">
@@ -6522,7 +6522,7 @@
         <v>543</v>
       </c>
       <c r="B535" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="536">
@@ -6530,7 +6530,7 @@
         <v>544</v>
       </c>
       <c r="B536" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="537">
@@ -6538,7 +6538,7 @@
         <v>545</v>
       </c>
       <c r="B537" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="538">
@@ -6546,7 +6546,7 @@
         <v>546</v>
       </c>
       <c r="B538" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="539">
@@ -6554,7 +6554,7 @@
         <v>547</v>
       </c>
       <c r="B539" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="540">
@@ -6562,7 +6562,7 @@
         <v>548</v>
       </c>
       <c r="B540" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="541">
@@ -6570,7 +6570,7 @@
         <v>549</v>
       </c>
       <c r="B541" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="542">
@@ -6586,7 +6586,7 @@
         <v>551</v>
       </c>
       <c r="B543" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="544">
@@ -6594,7 +6594,7 @@
         <v>552</v>
       </c>
       <c r="B544" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
     </row>
     <row r="545">
@@ -6610,7 +6610,7 @@
         <v>554</v>
       </c>
       <c r="B546" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="547">
@@ -6618,7 +6618,7 @@
         <v>555</v>
       </c>
       <c r="B547" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="548">
@@ -6634,7 +6634,7 @@
         <v>557</v>
       </c>
       <c r="B549" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="550">
@@ -6650,7 +6650,7 @@
         <v>559</v>
       </c>
       <c r="B551" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="552">
@@ -6658,7 +6658,7 @@
         <v>560</v>
       </c>
       <c r="B552" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="553">
@@ -6666,7 +6666,7 @@
         <v>561</v>
       </c>
       <c r="B553" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="554">
@@ -6674,7 +6674,7 @@
         <v>562</v>
       </c>
       <c r="B554" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="555">
@@ -6682,7 +6682,7 @@
         <v>563</v>
       </c>
       <c r="B555" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="556">
@@ -6690,7 +6690,7 @@
         <v>564</v>
       </c>
       <c r="B556" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="557">
@@ -6706,7 +6706,7 @@
         <v>566</v>
       </c>
       <c r="B558" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="559">
@@ -6722,7 +6722,7 @@
         <v>568</v>
       </c>
       <c r="B560" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="561">
@@ -6738,7 +6738,7 @@
         <v>570</v>
       </c>
       <c r="B562" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="563">
@@ -6746,7 +6746,7 @@
         <v>571</v>
       </c>
       <c r="B563" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="564">
@@ -6754,7 +6754,7 @@
         <v>572</v>
       </c>
       <c r="B564" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="565">
@@ -6762,7 +6762,7 @@
         <v>573</v>
       </c>
       <c r="B565" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="566">
@@ -6770,7 +6770,7 @@
         <v>574</v>
       </c>
       <c r="B566" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="567">
@@ -6778,7 +6778,7 @@
         <v>575</v>
       </c>
       <c r="B567" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="568">
@@ -6786,7 +6786,7 @@
         <v>576</v>
       </c>
       <c r="B568" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="569">
@@ -6802,7 +6802,7 @@
         <v>578</v>
       </c>
       <c r="B570" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="571">
@@ -6810,7 +6810,7 @@
         <v>579</v>
       </c>
       <c r="B571" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="572">
@@ -6818,7 +6818,7 @@
         <v>580</v>
       </c>
       <c r="B572" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="573">
@@ -6834,7 +6834,7 @@
         <v>582</v>
       </c>
       <c r="B574" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="575">
@@ -6842,7 +6842,7 @@
         <v>583</v>
       </c>
       <c r="B575" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="576">
@@ -6850,7 +6850,7 @@
         <v>584</v>
       </c>
       <c r="B576" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="577">
@@ -6866,7 +6866,7 @@
         <v>586</v>
       </c>
       <c r="B578" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="579">
@@ -6874,7 +6874,7 @@
         <v>587</v>
       </c>
       <c r="B579" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="580">
@@ -6882,7 +6882,7 @@
         <v>588</v>
       </c>
       <c r="B580" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="581">
@@ -6898,7 +6898,7 @@
         <v>590</v>
       </c>
       <c r="B582" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="583">
@@ -6906,7 +6906,7 @@
         <v>591</v>
       </c>
       <c r="B583" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="584">
@@ -6914,7 +6914,7 @@
         <v>592</v>
       </c>
       <c r="B584" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="585">
@@ -6922,7 +6922,7 @@
         <v>593</v>
       </c>
       <c r="B585" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="586">
@@ -6930,7 +6930,7 @@
         <v>594</v>
       </c>
       <c r="B586" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="587">
@@ -6938,7 +6938,7 @@
         <v>595</v>
       </c>
       <c r="B587" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="588">
@@ -6946,7 +6946,7 @@
         <v>596</v>
       </c>
       <c r="B588" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="589">
@@ -6954,7 +6954,7 @@
         <v>597</v>
       </c>
       <c r="B589" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="590">
@@ -6962,7 +6962,7 @@
         <v>598</v>
       </c>
       <c r="B590" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="591">
@@ -6970,7 +6970,7 @@
         <v>599</v>
       </c>
       <c r="B591" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="592">
@@ -6986,7 +6986,7 @@
         <v>601</v>
       </c>
       <c r="B593" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="594">
@@ -6994,7 +6994,7 @@
         <v>602</v>
       </c>
       <c r="B594" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="595">
@@ -7002,7 +7002,7 @@
         <v>603</v>
       </c>
       <c r="B595" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="596">
@@ -7018,7 +7018,7 @@
         <v>605</v>
       </c>
       <c r="B597" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="598">
@@ -7026,7 +7026,7 @@
         <v>606</v>
       </c>
       <c r="B598" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="599">
@@ -7034,7 +7034,7 @@
         <v>607</v>
       </c>
       <c r="B599" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="600">
@@ -7042,7 +7042,7 @@
         <v>608</v>
       </c>
       <c r="B600" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="601">
@@ -7050,7 +7050,7 @@
         <v>609</v>
       </c>
       <c r="B601" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="602">
@@ -7058,7 +7058,7 @@
         <v>610</v>
       </c>
       <c r="B602" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="603">
@@ -7066,7 +7066,7 @@
         <v>611</v>
       </c>
       <c r="B603" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="604">
@@ -7074,7 +7074,7 @@
         <v>612</v>
       </c>
       <c r="B604" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="605">
@@ -7082,7 +7082,7 @@
         <v>613</v>
       </c>
       <c r="B605" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="606">
@@ -7090,7 +7090,7 @@
         <v>614</v>
       </c>
       <c r="B606" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="607">
@@ -7098,7 +7098,7 @@
         <v>615</v>
       </c>
       <c r="B607" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="608">
@@ -7106,7 +7106,7 @@
         <v>616</v>
       </c>
       <c r="B608" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="609">
@@ -7114,7 +7114,7 @@
         <v>617</v>
       </c>
       <c r="B609" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="610">
@@ -7138,7 +7138,7 @@
         <v>620</v>
       </c>
       <c r="B612" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="613">
@@ -7146,7 +7146,7 @@
         <v>621</v>
       </c>
       <c r="B613" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="614">
@@ -7154,7 +7154,7 @@
         <v>622</v>
       </c>
       <c r="B614" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="615">
@@ -7178,7 +7178,7 @@
         <v>625</v>
       </c>
       <c r="B617" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="618">
@@ -7194,7 +7194,7 @@
         <v>627</v>
       </c>
       <c r="B619" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="620">
@@ -7202,7 +7202,7 @@
         <v>628</v>
       </c>
       <c r="B620" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="621">
@@ -7210,7 +7210,7 @@
         <v>629</v>
       </c>
       <c r="B621" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="622">
@@ -7218,7 +7218,7 @@
         <v>630</v>
       </c>
       <c r="B622" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="623">
@@ -7234,7 +7234,7 @@
         <v>632</v>
       </c>
       <c r="B624" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="625">
@@ -7242,7 +7242,7 @@
         <v>633</v>
       </c>
       <c r="B625" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="626">
